--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_metropolitana.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_metropolitana.xlsx
@@ -1,46 +1,263 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Cobertura_Comunal" sheetId="1" r:id="rId1"/>
+    <sheet name="Cobertura_Comunal" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cobertura_Comunal'!$A$1:$D$53</definedName>
+  </definedNames>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+  <si>
+    <t xml:space="preserve">comuna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residentes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proyectada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cobertura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiltil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilicura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estación Central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Independencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puente Alto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maipú</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pudahuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recoleta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santiago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo Barnechea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huechuraba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ñuñoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Bernardo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peñalolén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lampa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las Condes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vitacura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peñaflor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Pedro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Florida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Macul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Reina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conchalí</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo Prado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinta Normal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talagante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Bosque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerrillos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Pintana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Monte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melipilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isla de Maipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Providencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curacaví</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedro Aguirre Cerda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerro Navia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Joaquín</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Cisterna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San José de Maipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo Espejo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Padre Hurtado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Granja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Miguel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Ramón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">María Pinto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pirque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alhué</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calera de Tango</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha de creación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27 21:13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIT - MDSF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imagen asociada</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unidad territorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Año</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00135A"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,21 +265,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
@@ -112,10 +345,6 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -141,15 +370,12 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -175,6 +401,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -350,865 +577,832 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D53"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="21.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="12.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>comuna</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Residentes</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Proyectada</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Cobertura</t>
-        </is>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Tiltil</t>
-        </is>
-      </c>
-      <c r="B2">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="n">
         <v>10376</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2" t="n">
         <v>22262</v>
       </c>
-      <c r="D2">
-        <v>46.60857065852124</v>
+      <c r="D2" s="2" t="n">
+        <v>46.61</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Quilicura</t>
-        </is>
-      </c>
-      <c r="B3">
+      <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="n">
         <v>212320</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="2" t="n">
         <v>271385</v>
       </c>
-      <c r="D3">
-        <v>78.23571678611566</v>
+      <c r="D3" s="2" t="n">
+        <v>78.24</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Estación Central</t>
-        </is>
-      </c>
-      <c r="B4">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="n">
         <v>174310</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="2" t="n">
         <v>219897</v>
       </c>
-      <c r="D4">
-        <v>79.26893045380338</v>
+      <c r="D4" s="2" t="n">
+        <v>79.27</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Independencia</t>
-        </is>
-      </c>
-      <c r="B5">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="n">
         <v>122313</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="2" t="n">
         <v>151890</v>
       </c>
-      <c r="D5">
-        <v>80.52735532293107</v>
+      <c r="D5" s="2" t="n">
+        <v>80.53</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Puente Alto</t>
-        </is>
-      </c>
-      <c r="B6">
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="2" t="n">
         <v>563181</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="2" t="n">
         <v>664370</v>
       </c>
-      <c r="D6">
-        <v>84.76917982449538</v>
+      <c r="D6" s="2" t="n">
+        <v>84.77</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Colina</t>
-        </is>
-      </c>
-      <c r="B7">
+      <c r="A7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="2" t="n">
         <v>164279</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="2" t="n">
         <v>193594</v>
       </c>
-      <c r="D7">
-        <v>84.85748525264214</v>
+      <c r="D7" s="2" t="n">
+        <v>84.86</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Maipú</t>
-        </is>
-      </c>
-      <c r="B8">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="n">
         <v>499157</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="2" t="n">
         <v>586337</v>
       </c>
-      <c r="D8">
-        <v>85.13141759772964</v>
+      <c r="D8" s="2" t="n">
+        <v>85.13</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Pudahuel</t>
-        </is>
-      </c>
-      <c r="B9">
+      <c r="A9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="2" t="n">
         <v>224523</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="2" t="n">
         <v>260129</v>
       </c>
-      <c r="D9">
-        <v>86.31217588196625</v>
+      <c r="D9" s="2" t="n">
+        <v>86.31</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Recoleta</t>
-        </is>
-      </c>
-      <c r="B10">
+      <c r="A10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="2" t="n">
         <v>169527</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="2" t="n">
         <v>196073</v>
       </c>
-      <c r="D10">
-        <v>86.46116497426979</v>
+      <c r="D10" s="2" t="n">
+        <v>86.46</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Santiago</t>
-        </is>
-      </c>
-      <c r="B11">
+      <c r="A11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="2" t="n">
         <v>466501</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="2" t="n">
         <v>536089</v>
       </c>
-      <c r="D11">
-        <v>87.01931955328313</v>
+      <c r="D11" s="2" t="n">
+        <v>87.02</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Lo Barnechea</t>
-        </is>
-      </c>
-      <c r="B12">
+      <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="2" t="n">
         <v>113279</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="2" t="n">
         <v>129790</v>
       </c>
-      <c r="D12">
-        <v>87.27868094614377</v>
+      <c r="D12" s="2" t="n">
+        <v>87.28</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Huechuraba</t>
-        </is>
-      </c>
-      <c r="B13">
+      <c r="A13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="2" t="n">
         <v>103580</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="2" t="n">
         <v>117121</v>
       </c>
-      <c r="D13">
-        <v>88.43845254053501</v>
+      <c r="D13" s="2" t="n">
+        <v>88.44</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Ñuñoa</t>
-        </is>
-      </c>
-      <c r="B14">
+      <c r="A14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="2" t="n">
         <v>233625</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="2" t="n">
         <v>263319</v>
       </c>
-      <c r="D14">
-        <v>88.72318366695909</v>
+      <c r="D14" s="2" t="n">
+        <v>88.72</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>San Bernardo</t>
-        </is>
-      </c>
-      <c r="B15">
+      <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2" t="n">
         <v>307443</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="2" t="n">
         <v>345583</v>
       </c>
-      <c r="D15">
-        <v>88.96357749079093</v>
+      <c r="D15" s="2" t="n">
+        <v>88.96</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Peñalolén</t>
-        </is>
-      </c>
-      <c r="B16">
+      <c r="A16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="2" t="n">
         <v>242061</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="2" t="n">
         <v>271854</v>
       </c>
-      <c r="D16">
-        <v>89.04080866935928</v>
+      <c r="D16" s="2" t="n">
+        <v>89.04</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Lampa</t>
-        </is>
-      </c>
-      <c r="B17">
+      <c r="A17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="2" t="n">
         <v>124969</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="2" t="n">
         <v>139266</v>
       </c>
-      <c r="D17">
-        <v>89.73403415047463</v>
+      <c r="D17" s="2" t="n">
+        <v>89.73</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Las Condes</t>
-        </is>
-      </c>
-      <c r="B18">
+      <c r="A18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="2" t="n">
         <v>306439</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="2" t="n">
         <v>341183</v>
       </c>
-      <c r="D18">
-        <v>89.81660868214418</v>
+      <c r="D18" s="2" t="n">
+        <v>89.82</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Vitacura</t>
-        </is>
-      </c>
-      <c r="B19">
+      <c r="A19" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="2" t="n">
         <v>87564</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="2" t="n">
         <v>97388</v>
       </c>
-      <c r="D19">
-        <v>89.91251488889802</v>
+      <c r="D19" s="2" t="n">
+        <v>89.91</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Renca</t>
-        </is>
-      </c>
-      <c r="B20">
+      <c r="A20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="2" t="n">
         <v>148941</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="2" t="n">
         <v>162854</v>
       </c>
-      <c r="D20">
-        <v>91.45676495511317</v>
+      <c r="D20" s="2" t="n">
+        <v>91.46</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Peñaflor</t>
-        </is>
-      </c>
-      <c r="B21">
+      <c r="A21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="2" t="n">
         <v>96514</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="2" t="n">
         <v>105498</v>
       </c>
-      <c r="D21">
-        <v>91.48419875258298</v>
+      <c r="D21" s="2" t="n">
+        <v>91.48</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>San Pedro</t>
-        </is>
-      </c>
-      <c r="B22">
+      <c r="A22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="2" t="n">
         <v>11445</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="2" t="n">
         <v>12412</v>
       </c>
-      <c r="D22">
-        <v>92.20915243312923</v>
+      <c r="D22" s="2" t="n">
+        <v>92.21</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>La Florida</t>
-        </is>
-      </c>
-      <c r="B23">
+      <c r="A23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="2" t="n">
         <v>377737</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="2" t="n">
         <v>406796</v>
       </c>
-      <c r="D23">
-        <v>92.85661609258695</v>
+      <c r="D23" s="2" t="n">
+        <v>92.86</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Macul</t>
-        </is>
-      </c>
-      <c r="B24">
+      <c r="A24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="2" t="n">
         <v>128078</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="2" t="n">
         <v>137735</v>
       </c>
-      <c r="D24">
-        <v>92.98871020437797</v>
+      <c r="D24" s="2" t="n">
+        <v>92.99</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>La Reina</t>
-        </is>
-      </c>
-      <c r="B25">
+      <c r="A25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" s="2" t="n">
         <v>93241</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="2" t="n">
         <v>99686</v>
       </c>
-      <c r="D25">
-        <v>93.53469895471781</v>
+      <c r="D25" s="2" t="n">
+        <v>93.53</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Paine</t>
-        </is>
-      </c>
-      <c r="B26">
+      <c r="A26" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="2" t="n">
         <v>81437</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="2" t="n">
         <v>87059</v>
       </c>
-      <c r="D26">
-        <v>93.54231038720867</v>
+      <c r="D26" s="2" t="n">
+        <v>93.54</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Conchalí</t>
-        </is>
-      </c>
-      <c r="B27">
+      <c r="A27" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="2" t="n">
         <v>129086</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="2" t="n">
         <v>137678</v>
       </c>
-      <c r="D27">
-        <v>93.75935153038249</v>
+      <c r="D27" s="2" t="n">
+        <v>93.76</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Lo Prado</t>
-        </is>
-      </c>
-      <c r="B28">
+      <c r="A28" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="2" t="n">
         <v>96529</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="2" t="n">
         <v>102923</v>
       </c>
-      <c r="D28">
-        <v>93.78758877996172</v>
+      <c r="D28" s="2" t="n">
+        <v>93.79</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Quinta Normal</t>
-        </is>
-      </c>
-      <c r="B29">
+      <c r="A29" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" s="2" t="n">
         <v>132329</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="2" t="n">
         <v>140964</v>
       </c>
-      <c r="D29">
-        <v>93.87432252206237</v>
+      <c r="D29" s="2" t="n">
+        <v>93.87</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Talagante</t>
-        </is>
-      </c>
-      <c r="B30">
+      <c r="A30" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="2" t="n">
         <v>80549</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="2" t="n">
         <v>84670</v>
       </c>
-      <c r="D30">
-        <v>95.13286878469351</v>
+      <c r="D30" s="2" t="n">
+        <v>95.13</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>El Bosque</t>
-        </is>
-      </c>
-      <c r="B31">
+      <c r="A31" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" s="2" t="n">
         <v>162335</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="2" t="n">
         <v>170536</v>
       </c>
-      <c r="D31">
-        <v>95.19104470610311</v>
+      <c r="D31" s="2" t="n">
+        <v>95.19</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Cerrillos</t>
-        </is>
-      </c>
-      <c r="B32">
+      <c r="A32" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="2" t="n">
         <v>85810</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="2" t="n">
         <v>90060</v>
       </c>
-      <c r="D32">
-        <v>95.28092382855874</v>
+      <c r="D32" s="2" t="n">
+        <v>95.28</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>La Pintana</t>
-        </is>
-      </c>
-      <c r="B33">
+      <c r="A33" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="2" t="n">
         <v>181775</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="2" t="n">
         <v>189151</v>
       </c>
-      <c r="D33">
-        <v>96.10046999487182</v>
+      <c r="D33" s="2" t="n">
+        <v>96.1</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>El Monte</t>
-        </is>
-      </c>
-      <c r="B34">
+      <c r="A34" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" s="2" t="n">
         <v>40277</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="2" t="n">
         <v>41711</v>
       </c>
-      <c r="D34">
-        <v>96.56205797031959</v>
+      <c r="D34" s="2" t="n">
+        <v>96.56</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Melipilla</t>
-        </is>
-      </c>
-      <c r="B35">
+      <c r="A35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="2" t="n">
         <v>143846</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="2" t="n">
         <v>147275</v>
       </c>
-      <c r="D35">
-        <v>97.67170259718215</v>
+      <c r="D35" s="2" t="n">
+        <v>97.67</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Isla de Maipo</t>
-        </is>
-      </c>
-      <c r="B36">
+      <c r="A36" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="2" t="n">
         <v>41149</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="2" t="n">
         <v>41876</v>
       </c>
-      <c r="D36">
-        <v>98.2639220555927</v>
+      <c r="D36" s="2" t="n">
+        <v>98.26</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Providencia</t>
-        </is>
-      </c>
-      <c r="B37">
+      <c r="A37" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="2" t="n">
         <v>161152</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="2" t="n">
         <v>162837</v>
       </c>
-      <c r="D37">
-        <v>98.96522289160326</v>
+      <c r="D37" s="2" t="n">
+        <v>98.97</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Curacaví</t>
-        </is>
-      </c>
-      <c r="B38">
+      <c r="A38" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="2" t="n">
         <v>37767</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="2" t="n">
         <v>37932</v>
       </c>
-      <c r="D38">
-        <v>99.56501107244543</v>
+      <c r="D38" s="2" t="n">
+        <v>99.57</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Pedro Aguirre Cerda</t>
-        </is>
-      </c>
-      <c r="B39">
+      <c r="A39" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="2" t="n">
         <v>105257</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="2" t="n">
         <v>105483</v>
       </c>
-      <c r="D39">
-        <v>99.78574746641638</v>
+      <c r="D39" s="2" t="n">
+        <v>99.79</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Cerro Navia</t>
-        </is>
-      </c>
-      <c r="B40">
+      <c r="A40" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="2" t="n">
         <v>140544</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="2" t="n">
         <v>140581</v>
       </c>
-      <c r="D40">
-        <v>99.97368065385793</v>
+      <c r="D40" s="2" t="n">
+        <v>99.97</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>San Joaquín</t>
-        </is>
-      </c>
-      <c r="B41">
+      <c r="A41" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="2" t="n">
         <v>103925</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="2" t="n">
         <v>103420</v>
       </c>
-      <c r="D41">
-        <v>100.4883001353703</v>
+      <c r="D41" s="2" t="n">
+        <v>100.49</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>La Cisterna</t>
-        </is>
-      </c>
-      <c r="B42">
+      <c r="A42" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="2" t="n">
         <v>102378</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="2" t="n">
         <v>101377</v>
       </c>
-      <c r="D42">
-        <v>100.9874034544325</v>
+      <c r="D42" s="2" t="n">
+        <v>100.99</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>San José de Maipo</t>
-        </is>
-      </c>
-      <c r="B43">
+      <c r="A43" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="2" t="n">
         <v>19543</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="2" t="n">
         <v>19330</v>
       </c>
-      <c r="D43">
-        <v>101.1019141231247</v>
+      <c r="D43" s="2" t="n">
+        <v>101.1</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Lo Espejo</t>
-        </is>
-      </c>
-      <c r="B44">
+      <c r="A44" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B44" s="2" t="n">
         <v>102921</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="2" t="n">
         <v>101615</v>
       </c>
-      <c r="D44">
-        <v>101.2852433203759</v>
+      <c r="D44" s="2" t="n">
+        <v>101.29</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Padre Hurtado</t>
-        </is>
-      </c>
-      <c r="B45">
+      <c r="A45" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B45" s="2" t="n">
         <v>81009</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="2" t="n">
         <v>79925</v>
       </c>
-      <c r="D45">
-        <v>101.3562715045355</v>
+      <c r="D45" s="2" t="n">
+        <v>101.36</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>La Granja</t>
-        </is>
-      </c>
-      <c r="B46">
+      <c r="A46" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B46" s="2" t="n">
         <v>123172</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="2" t="n">
         <v>120249</v>
       </c>
-      <c r="D46">
-        <v>102.4307894452345</v>
+      <c r="D46" s="2" t="n">
+        <v>102.43</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Buin</t>
-        </is>
-      </c>
-      <c r="B47">
+      <c r="A47" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B47" s="2" t="n">
         <v>118985</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="2" t="n">
         <v>116032</v>
       </c>
-      <c r="D47">
-        <v>102.5449875896304</v>
+      <c r="D47" s="2" t="n">
+        <v>102.54</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>San Miguel</t>
-        </is>
-      </c>
-      <c r="B48">
+      <c r="A48" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B48" s="2" t="n">
         <v>146220</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="2" t="n">
         <v>142549</v>
       </c>
-      <c r="D48">
-        <v>102.5752548246568</v>
+      <c r="D48" s="2" t="n">
+        <v>102.58</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>San Ramón</t>
-        </is>
-      </c>
-      <c r="B49">
+      <c r="A49" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B49" s="2" t="n">
         <v>88813</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="2" t="n">
         <v>84495</v>
       </c>
-      <c r="D49">
-        <v>105.1103615598556</v>
+      <c r="D49" s="2" t="n">
+        <v>105.11</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>María Pinto</t>
-        </is>
-      </c>
-      <c r="B50">
+      <c r="A50" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B50" s="2" t="n">
         <v>16607</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="2" t="n">
         <v>15503</v>
       </c>
-      <c r="D50">
-        <v>107.1212023479327</v>
+      <c r="D50" s="2" t="n">
+        <v>107.12</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Pirque</t>
-        </is>
-      </c>
-      <c r="B51">
+      <c r="A51" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B51" s="2" t="n">
         <v>35594</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="2" t="n">
         <v>32412</v>
       </c>
-      <c r="D51">
-        <v>109.8173515981735</v>
+      <c r="D51" s="2" t="n">
+        <v>109.82</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Alhué</t>
-        </is>
-      </c>
-      <c r="B52">
+      <c r="A52" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B52" s="2" t="n">
         <v>8740</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="2" t="n">
         <v>7756</v>
       </c>
-      <c r="D52">
-        <v>112.6869520371325</v>
+      <c r="D52" s="2" t="n">
+        <v>112.69</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Calera de Tango</t>
-        </is>
-      </c>
-      <c r="B53">
+      <c r="A53" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B53" s="2" t="n">
         <v>35422</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="2" t="n">
         <v>29880</v>
       </c>
-      <c r="D53">
-        <v>118.5475234270415</v>
+      <c r="D53" s="2" t="n">
+        <v>118.55</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D53"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="24.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="60.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_metropolitana.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_metropolitana.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <si>
     <t xml:space="preserve">comuna</t>
   </si>
@@ -195,7 +195,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 21:13</t>
+    <t xml:space="preserve">2026-08-07 07:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -207,16 +207,25 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">plot_comunal_cobertura_2023_metropolitana.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Cobertura de residentes (comunal)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Region de Metropolitana</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023</t>
   </si>
 </sst>
 </file>
@@ -1382,23 +1391,23 @@
         <v>64</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_metropolitana.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_metropolitana.xlsx
@@ -195,7 +195,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-07 07:12</t>
+    <t xml:space="preserve">2026-08-28 11:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_metropolitana.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_metropolitana.xlsx
@@ -195,7 +195,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:12</t>
+    <t xml:space="preserve">2026-09-01 13:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_metropolitana.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_metropolitana.xlsx
@@ -195,7 +195,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-01 13:21</t>
+    <t xml:space="preserve">2026-09-06 17:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_metropolitana.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_metropolitana.xlsx
@@ -195,7 +195,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:17</t>
+    <t xml:space="preserve">2026-09-08 13:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
